--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.73868600295191</v>
+        <v>4.020036475479685</v>
       </c>
       <c r="D2" t="n">
-        <v>24.79792913605537</v>
+        <v>4.029663484608998</v>
       </c>
       <c r="E2" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F2" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.9368479223932</v>
+        <v>5.677237787388895</v>
       </c>
       <c r="D3" t="n">
-        <v>34.95747095274483</v>
+        <v>5.680589029821035</v>
       </c>
       <c r="E3" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F3" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.59499162651333</v>
+        <v>4.809186139308417</v>
       </c>
       <c r="D4" t="n">
-        <v>29.55949567014785</v>
+        <v>4.803418046399025</v>
       </c>
       <c r="E4" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F4" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.06107512165253</v>
+        <v>3.259924707268536</v>
       </c>
       <c r="D5" t="n">
-        <v>20.2620532376993</v>
+        <v>3.292583651126136</v>
       </c>
       <c r="E5" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F5" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.86700773434678</v>
+        <v>6.315888756831352</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80902476933609</v>
+        <v>6.306466525017115</v>
       </c>
       <c r="E6" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F6" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.44380793514568</v>
+        <v>6.084618789461174</v>
       </c>
       <c r="D7" t="n">
-        <v>36.84907606104288</v>
+        <v>5.987974859919468</v>
       </c>
       <c r="E7" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F7" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.94739784166438</v>
+        <v>4.866452149270462</v>
       </c>
       <c r="D8" t="n">
-        <v>29.485237378829</v>
+        <v>4.791351074059713</v>
       </c>
       <c r="E8" t="n">
-        <v>6.331026819343759</v>
+        <v>1.028791858143361</v>
       </c>
       <c r="F8" t="n">
-        <v>6.190435429675717</v>
+        <v>1.005945757322304</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
